--- a/data/processed/harmonization/Physical__Clay_content/10.5440_1854940/10.5440_1854940_soil_Physical__Clay_content.xlsx
+++ b/data/processed/harmonization/Physical__Clay_content/10.5440_1854940/10.5440_1854940_soil_Physical__Clay_content.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:172</t>
+          <t>TL_MM27:17-23.5:172</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:185</t>
+          <t>TL_MM27:14.5-20.5:185</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:167</t>
+          <t>TL_MM27:10-17:167</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:175</t>
+          <t>TL_MM27:12-18:175</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>TL_MM27:170</t>
+          <t>TL_MM27:12-18:170</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:188</t>
+          <t>KG_MM64:12.5-18.75:188</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:190</t>
+          <t>KG_MM64:6.25-12.5:190</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:192</t>
+          <t>KG_MM64:12.5-18.75:192</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>KG_MM64:140</t>
+          <t>KG_MM64:12.5-18.75:140</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Site:Soil_Sample_ID</t>
+          <t>Site:depth:Soil_Sample_ID</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
